--- a/datos/indicadores_adelantados/manufactura/utilizacion_capacidad_instalada_2017_2025.xlsx
+++ b/datos/indicadores_adelantados/manufactura/utilizacion_capacidad_instalada_2017_2025.xlsx
@@ -5,18 +5,18 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\1. Página Web\2026 - 03. Marzo\Manufactura 12-25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svrtruenasine.ine.gov.bo\UEIE-2024\1. Página Web\2026 - 06. Junio\Manufactura 01-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCACAC3-D550-427F-A633-2AA8920DE355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A991E3B-3033-4B01-BF47-04520FDCC1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cuadro_1" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">cuadro_1!$B$1:$T$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">cuadro_1!$B$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
   <si>
     <t xml:space="preserve">   Nota: La muestra utilizada para los índices, corresponde principalmente a empresas grandes y medianas.</t>
   </si>
@@ -111,9 +111,6 @@
     </r>
   </si>
   <si>
-    <t>BOLIVIA: PORCENTAJE DE UTILIZACIÓN DE LA CAPACIDAD PRODUCTIVA INSTALADA DE LA INDUSTRIA MANUFACTURERA SEGÚN TRIMESTRE 2017 - 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">   I    Trimestre </t>
   </si>
   <si>
@@ -142,19 +139,39 @@
     <t xml:space="preserve"> 
 INDUSTRIA DE ALIMENTOS Y BEBIDAS</t>
   </si>
+  <si>
+    <t>BOLIVIA: PORCENTAJE DE UTILIZACIÓN DE LA CAPACIDAD PRODUCTIVA INSTALADA DE LA INDUSTRIA MANUFACTURERA SEGÚN TRIMESTRE 2017 - 2026</t>
+  </si>
+  <si>
+    <r>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(p)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   II    Trimestre </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
     <numFmt numFmtId="166" formatCode="#,##0.0\ _€;\-#,##0.0\ _€"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00000000\ _€;\-#,##0.00000000\ _€"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Courier"/>
@@ -266,12 +283,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Garamond"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -376,16 +387,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -413,7 +420,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -436,9 +443,6 @@
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,19 +473,13 @@
     <xf numFmtId="166" fontId="15" fillId="4" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
@@ -534,20 +532,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38099</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1611631" cy="895350"/>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>983243</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8BE38F7-338F-495B-AED3-3D693C037718}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1745169-50C3-4CA0-A64E-09B7D5F5FC05}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -563,8 +566,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38099" y="47625"/>
-          <a:ext cx="1611631" cy="895350"/>
+          <a:off x="171450" y="1"/>
+          <a:ext cx="2867025" cy="983242"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -572,7 +575,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -932,31 +935,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AA62"/>
+  <dimension ref="B1:T66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.21875" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.88671875" style="2" customWidth="1"/>
     <col min="3" max="5" width="17" style="2" customWidth="1"/>
-    <col min="6" max="9" width="6.21875" style="2" customWidth="1"/>
-    <col min="10" max="12" width="13" style="2" customWidth="1"/>
-    <col min="13" max="14" width="6.21875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="6.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="6.21875" style="2" customWidth="1"/>
-    <col min="25" max="30" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="5.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="6.21875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="6.21875" style="2" customWidth="1"/>
+    <col min="18" max="23" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="83.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+    <row r="1" spans="2:20" ht="83.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -970,16 +972,9 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-    </row>
-    <row r="3" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="22" t="s">
+    </row>
+    <row r="3" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="18" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="5"/>
@@ -998,26 +993,19 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-    </row>
-    <row r="4" spans="2:27" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="4" spans="2:20" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1032,27 +1020,20 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-    </row>
-    <row r="5" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="11">
+    </row>
+    <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="10">
         <v>2017</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>AVERAGE(C6:C9)</f>
         <v>74.016389407276918</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>AVERAGE(D6:D9)</f>
         <v>68.939504015127284</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <f>AVERAGE(E6:E9)</f>
         <v>78.083747476180136</v>
       </c>
@@ -1069,25 +1050,18 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-    </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="14">
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="13">
         <v>73.182924991922803</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>67.165618709712049</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>77.981766568118843</v>
       </c>
       <c r="F6" s="4"/>
@@ -1103,82 +1077,68 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-    </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="14">
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="13">
         <v>75.367667909219875</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>71.824862342619411</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>78.194373514820754</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="14">
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="13">
         <v>74.733209151644218</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>70.219130678672016</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>78.338707422260356</v>
       </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14">
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="13">
         <v>72.781755576320762</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>66.548404329505658</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>77.820142399520591</v>
       </c>
       <c r="F9" s="7"/>
@@ -1196,19 +1156,12 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B10" s="16"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B10" s="15"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
@@ -1224,27 +1177,20 @@
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B11" s="17">
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="16">
         <v>2018</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <f>AVERAGE(C12:C15)</f>
         <v>72.892871455050084</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>AVERAGE(D12:D15)</f>
         <v>67.783419837331436</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <f>AVERAGE(E12:E15)</f>
         <v>76.962681398479177</v>
       </c>
@@ -1263,25 +1209,18 @@
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-    </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B12" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="14">
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13">
         <v>71.078869858003799</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>65.084459099912522</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <v>75.853047440085561</v>
       </c>
       <c r="F12" s="7"/>
@@ -1299,681 +1238,680 @@
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-    </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B13" s="13" t="s">
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="13">
+        <v>72.556611455647342</v>
+      </c>
+      <c r="D13" s="14">
+        <v>67.048988864956598</v>
+      </c>
+      <c r="E13" s="14">
+        <v>76.93476408292004</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B14" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="14">
-        <v>72.556611455647342</v>
-      </c>
-      <c r="D13" s="15">
-        <v>67.048988864956598</v>
-      </c>
-      <c r="E13" s="15">
-        <v>76.93476408292004</v>
-      </c>
-    </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
+      <c r="C14" s="13">
+        <v>74.604151142092675</v>
+      </c>
+      <c r="D14" s="14">
+        <v>68.085617326939882</v>
+      </c>
+      <c r="E14" s="14">
+        <v>79.808644745586093</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="14">
-        <v>74.604151142092675</v>
-      </c>
-      <c r="D14" s="15">
-        <v>68.085617326939882</v>
-      </c>
-      <c r="E14" s="15">
-        <v>79.808644745586093</v>
-      </c>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <v>73.331853364456478</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>70.914614057516758</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <v>75.254269325325012</v>
       </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B16" s="16"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B16" s="15"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="17">
+      <c r="B17" s="16">
         <v>2019</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>AVERAGE(C18:C21)</f>
         <v>70.751455476186678</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>AVERAGE(D18:D21)</f>
         <v>64.884686906393725</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <f>AVERAGE(E18:E21)</f>
         <v>74.960564671782834</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="13">
+        <v>70.360476322878398</v>
+      </c>
+      <c r="D18" s="14">
+        <v>66.807046138441208</v>
+      </c>
+      <c r="E18" s="14">
+        <v>72.901021918966677</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="14">
-        <v>70.360476322878398</v>
-      </c>
-      <c r="D18" s="15">
-        <v>66.807046138441208</v>
-      </c>
-      <c r="E18" s="15">
-        <v>72.901021918966677</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="13">
+        <v>69.234237361198979</v>
+      </c>
+      <c r="D19" s="14">
+        <v>63.325882435904482</v>
+      </c>
+      <c r="E19" s="14">
+        <v>73.486010437641028</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="14">
-        <v>69.234237361198979</v>
-      </c>
-      <c r="D19" s="15">
-        <v>63.325882435904482</v>
-      </c>
-      <c r="E19" s="15">
-        <v>73.486010437641028</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="13" t="s">
+      <c r="C20" s="13">
+        <v>72.005645563862473</v>
+      </c>
+      <c r="D20" s="14">
+        <v>64.128713623133621</v>
+      </c>
+      <c r="E20" s="14">
+        <v>77.663698859205567</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="14">
-        <v>72.005645563862473</v>
-      </c>
-      <c r="D20" s="15">
-        <v>64.128713623133621</v>
-      </c>
-      <c r="E20" s="15">
-        <v>77.663698859205567</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <v>71.405462656806904</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <v>65.277105428095595</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <v>75.791527471318076</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="16"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>2020</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>AVERAGE(C24:C27)</f>
         <v>67.262767412317814</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>AVERAGE(D24:D27)</f>
         <v>63.193270351021077</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="11">
         <f>AVERAGE(E24:E27)</f>
         <v>70.571249873702214</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="13">
+        <v>68.479017917247617</v>
+      </c>
+      <c r="D24" s="14">
+        <v>62.40671837438461</v>
+      </c>
+      <c r="E24" s="14">
+        <v>73.396619989074509</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="14">
-        <v>68.479017917247617</v>
-      </c>
-      <c r="D24" s="15">
-        <v>62.40671837438461</v>
-      </c>
-      <c r="E24" s="15">
-        <v>73.396619989074509</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="13">
+        <v>62.617339694484173</v>
+      </c>
+      <c r="D25" s="14">
+        <v>62.435627687289163</v>
+      </c>
+      <c r="E25" s="14">
+        <v>62.793922667568111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="14">
-        <v>62.617339694484173</v>
-      </c>
-      <c r="D25" s="15">
-        <v>62.435627687289163</v>
-      </c>
-      <c r="E25" s="15">
-        <v>62.793922667568111</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="13" t="s">
+      <c r="C26" s="13">
+        <v>68.508132352375455</v>
+      </c>
+      <c r="D26" s="14">
+        <v>63.726175687185162</v>
+      </c>
+      <c r="E26" s="14">
+        <v>72.383681347991441</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="14">
-        <v>68.508132352375455</v>
-      </c>
-      <c r="D26" s="15">
-        <v>63.726175687185162</v>
-      </c>
-      <c r="E26" s="15">
-        <v>72.383681347991441</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <v>69.446579685164011</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <v>64.204559655225381</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <v>73.710775490174768</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="16"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>2021</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>AVERAGE(C30:C33)</f>
         <v>68.716007326066944</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>AVERAGE(D30:D33)</f>
         <v>67.230345504697993</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="11">
         <f>AVERAGE(E30:E33)</f>
         <v>70.411609355888473</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="13">
+        <v>66.654436429984628</v>
+      </c>
+      <c r="D30" s="14">
+        <v>62.705212087818239</v>
+      </c>
+      <c r="E30" s="14">
+        <v>71.174050492594191</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="14">
-        <v>66.654436429984628</v>
-      </c>
-      <c r="D30" s="15">
-        <v>62.705212087818239</v>
-      </c>
-      <c r="E30" s="15">
-        <v>71.174050492594191</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="13" t="s">
+      <c r="C31" s="13">
+        <v>67.012285413158097</v>
+      </c>
+      <c r="D31" s="14">
+        <v>63.52133692608907</v>
+      </c>
+      <c r="E31" s="14">
+        <v>71.001256429145059</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="14">
-        <v>67.012285413158097</v>
-      </c>
-      <c r="D31" s="15">
-        <v>63.52133692608907</v>
-      </c>
-      <c r="E31" s="15">
-        <v>71.001256429145059</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" s="13" t="s">
+      <c r="C32" s="13">
+        <v>71.341963459773737</v>
+      </c>
+      <c r="D32" s="14">
+        <v>71.519607714544605</v>
+      </c>
+      <c r="E32" s="14">
+        <v>71.130156781854453</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="14">
-        <v>71.341963459773737</v>
-      </c>
-      <c r="D32" s="15">
-        <v>71.519607714544605</v>
-      </c>
-      <c r="E32" s="15">
-        <v>71.130156781854453</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13">
         <v>69.855344001351298</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <v>71.17522529034008</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="14">
         <v>68.340973719960161</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="16"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="17">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="15"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="16">
         <v>2022</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <f>AVERAGE(C36:C39)</f>
         <v>70.45336473994017</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <f>AVERAGE(D36:D39)</f>
         <v>69.862591128501961</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="11">
         <f>AVERAGE(E36:E39)</f>
         <v>71.15707216601416</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="13" t="s">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="13">
+        <v>71.113374859618801</v>
+      </c>
+      <c r="D36" s="14">
+        <v>69.326570888827206</v>
+      </c>
+      <c r="E36" s="14">
+        <v>73.25073143453541</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="14">
-        <v>71.113374859618801</v>
-      </c>
-      <c r="D36" s="15">
-        <v>69.326570888827206</v>
-      </c>
-      <c r="E36" s="15">
-        <v>73.25073143453541</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="13" t="s">
+      <c r="C37" s="13">
+        <v>72.425277362166156</v>
+      </c>
+      <c r="D37" s="14">
+        <v>71.63264491365743</v>
+      </c>
+      <c r="E37" s="14">
+        <v>73.376147641388783</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="14">
-        <v>72.425277362166156</v>
-      </c>
-      <c r="D37" s="15">
-        <v>71.63264491365743</v>
-      </c>
-      <c r="E37" s="15">
-        <v>73.376147641388783</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="13" t="s">
+      <c r="C38" s="13">
+        <v>69.984393519563952</v>
+      </c>
+      <c r="D38" s="14">
+        <v>72.358143142999282</v>
+      </c>
+      <c r="E38" s="14">
+        <v>67.134946536824259</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="14">
-        <v>69.984393519563952</v>
-      </c>
-      <c r="D38" s="15">
-        <v>72.358143142999282</v>
-      </c>
-      <c r="E38" s="15">
-        <v>67.134946536824259</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="14">
+      <c r="C39" s="13">
         <v>68.290413218411771</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <v>66.133005568523927</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>70.866463051308202</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="16"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="17" t="s">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="15"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="11">
         <f>AVERAGE(C42:C45)</f>
         <v>71.45694697770314</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="11">
         <f>AVERAGE(D42:D45)</f>
         <v>73.465712753821947</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="11">
         <f>AVERAGE(E42:E45)</f>
         <v>69.436602225495108</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="13" t="s">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="13">
+        <v>68.932986666947684</v>
+      </c>
+      <c r="D42" s="14">
+        <v>69.787980877288504</v>
+      </c>
+      <c r="E42" s="14">
+        <v>68.073064078377968</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="14">
-        <v>68.932986666947684</v>
-      </c>
-      <c r="D42" s="15">
-        <v>69.787980877288504</v>
-      </c>
-      <c r="E42" s="15">
-        <v>68.073064078377968</v>
-      </c>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="13" t="s">
+      <c r="C43" s="13">
+        <v>72.688105767658172</v>
+      </c>
+      <c r="D43" s="14">
+        <v>78.035147858082667</v>
+      </c>
+      <c r="E43" s="14">
+        <v>67.310242128375521</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="14">
-        <v>72.688105767658172</v>
-      </c>
-      <c r="D43" s="15">
-        <v>78.035147858082667</v>
-      </c>
-      <c r="E43" s="15">
-        <v>67.310242128375521</v>
-      </c>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="13" t="s">
+      <c r="C44" s="13">
+        <v>72.762036828468339</v>
+      </c>
+      <c r="D44" s="14">
+        <v>73.453765372863984</v>
+      </c>
+      <c r="E44" s="14">
+        <v>72.066321005729478</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="14">
-        <v>72.762036828468339</v>
-      </c>
-      <c r="D44" s="15">
-        <v>73.453765372863984</v>
-      </c>
-      <c r="E44" s="15">
-        <v>72.066321005729478</v>
-      </c>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="14">
+      <c r="C45" s="13">
         <v>71.444658647738379</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="14">
         <v>72.585956907052605</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>70.296781689497465</v>
       </c>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="16"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="17" t="s">
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="15"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <f>AVERAGE(C48:C51)</f>
         <v>68.557525195672781</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="11">
         <f>AVERAGE(D48:D51)</f>
         <v>68.098978180787725</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="11">
         <f>AVERAGE(E48:E51)</f>
         <v>69.041953416173712</v>
       </c>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="13" t="s">
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="13">
+        <v>70.214266151248523</v>
+      </c>
+      <c r="D48" s="14">
+        <v>70.405975989946555</v>
+      </c>
+      <c r="E48" s="14">
+        <v>70.011735869732661</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="14">
-        <v>70.214266151248523</v>
-      </c>
-      <c r="D48" s="15">
-        <v>70.405975989946555</v>
-      </c>
-      <c r="E48" s="15">
-        <v>70.011735869732661</v>
-      </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="13" t="s">
+      <c r="C49" s="13">
+        <v>69.620986102849869</v>
+      </c>
+      <c r="D49" s="14">
+        <v>70.750800068252843</v>
+      </c>
+      <c r="E49" s="14">
+        <v>68.427403436317107</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="14">
-        <v>69.620986102849869</v>
-      </c>
-      <c r="D49" s="15">
-        <v>70.750800068252843</v>
-      </c>
-      <c r="E49" s="15">
-        <v>68.427403436317107</v>
-      </c>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="13" t="s">
+      <c r="C50" s="13">
+        <v>71.015264056593807</v>
+      </c>
+      <c r="D50" s="14">
+        <v>71.525511987870203</v>
+      </c>
+      <c r="E50" s="14">
+        <v>70.476216828417321</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="14">
-        <v>71.015264056593807</v>
-      </c>
-      <c r="D50" s="15">
-        <v>71.525511987870203</v>
-      </c>
-      <c r="E50" s="15">
-        <v>70.476216828417321</v>
-      </c>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="14">
+      <c r="C51" s="13">
         <v>63.379584471998882</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="14">
         <v>59.713624677081292</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="14">
         <v>67.252457530227801</v>
       </c>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="16"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="17" t="s">
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="15"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <f>AVERAGE(C54:C57)</f>
         <v>68.03787824297774</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="11">
         <f>AVERAGE(D54:D57)</f>
         <v>70.657320949140967</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="11">
         <f>AVERAGE(E54:E57)</f>
         <v>65.169259190560226</v>
       </c>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="13" t="s">
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B54" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="13">
+        <v>63.092483277655667</v>
+      </c>
+      <c r="D54" s="14">
+        <v>65.311355017390085</v>
+      </c>
+      <c r="E54" s="14">
+        <v>60.662539789104898</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="14">
-        <v>63.092483277655667</v>
-      </c>
-      <c r="D54" s="15">
-        <v>65.311355017390085</v>
-      </c>
-      <c r="E54" s="15">
-        <v>60.662539789104898</v>
-      </c>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B55" s="13" t="s">
+      <c r="C55" s="13">
+        <v>69.536676648611675</v>
+      </c>
+      <c r="D55" s="14">
+        <v>70.481428340659008</v>
+      </c>
+      <c r="E55" s="14">
+        <v>68.502054781435916</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="14">
-        <v>69.536676648611675</v>
-      </c>
-      <c r="D55" s="15">
-        <v>70.481428340659008</v>
-      </c>
-      <c r="E55" s="15">
-        <v>68.502054781435916</v>
-      </c>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="14">
+      <c r="C56" s="13">
         <v>70.728472963168215</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="14">
         <v>75.481130473749531</v>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="14">
         <v>65.523715534272824</v>
       </c>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="20">
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="13">
         <v>68.793880082475454</v>
       </c>
-      <c r="D57" s="21">
+      <c r="D57" s="14">
         <v>71.355369964765231</v>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="14">
         <v>65.98872665742725</v>
       </c>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-    </row>
-    <row r="58" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="6" t="s">
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B58" s="15"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B59" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="11">
+        <f>AVERAGE(C61:C64)</f>
+        <v>61.851034123892298</v>
+      </c>
+      <c r="D59" s="11">
+        <f>AVERAGE(D61:D64)</f>
+        <v>65.589341557790661</v>
+      </c>
+      <c r="E59" s="11">
+        <f>AVERAGE(E61:E64)</f>
+        <v>57.485470137318607</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B60" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="13">
+        <v>64.790880829072165</v>
+      </c>
+      <c r="D60" s="14">
+        <v>65.239043009704261</v>
+      </c>
+      <c r="E60" s="14">
+        <v>64.267520803042544</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="13">
+        <v>61.851034123892298</v>
+      </c>
+      <c r="D61" s="14">
+        <v>65.589341557790661</v>
+      </c>
+      <c r="E61" s="14">
+        <v>57.485470137318607</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" spans="2:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="6" t="s">
+    <row r="64" spans="2:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="21"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
